--- a/income-expense-template.xlsx
+++ b/income-expense-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bsayedy/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9379A4-E040-DB42-9FDC-2A7346652EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6119A8A5-DCB4-9540-86D5-81ADB8681D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{4964DFDE-59A9-CF4B-9057-9716C5A32404}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{4964DFDE-59A9-CF4B-9057-9716C5A32404}"/>
   </bookViews>
   <sheets>
     <sheet name="income-expense-template " sheetId="1" r:id="rId1"/>
@@ -450,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -565,6 +565,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -611,10 +640,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -661,7 +697,7 @@
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -680,6 +716,47 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -718,6 +795,45 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -756,6 +872,45 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -794,66 +949,55 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -887,12 +1031,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57952CBF-CB75-FC47-AF2C-FB253775E2C9}" name="Table1" displayName="Table1" ref="A1:M10" totalsRowShown="0" dataDxfId="11" dataCellStyle="Currency">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57952CBF-CB75-FC47-AF2C-FB253775E2C9}" name="Table1" displayName="Table1" ref="A1:M10" totalsRowShown="0" dataDxfId="13" dataCellStyle="Currency">
   <autoFilter ref="A1:M10" xr:uid="{57952CBF-CB75-FC47-AF2C-FB253775E2C9}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{4DEBBB6C-CF16-D944-933C-D8BF72F8222D}" name="Date" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{85166C7B-35FD-434A-A48C-5AA331E54576}" name="Category"/>
-    <tableColumn id="3" xr3:uid="{0621A243-DBFA-E64B-8B5F-01A1550A3158}" name="Item"/>
+    <tableColumn id="1" xr3:uid="{4DEBBB6C-CF16-D944-933C-D8BF72F8222D}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{85166C7B-35FD-434A-A48C-5AA331E54576}" name="Category" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{0621A243-DBFA-E64B-8B5F-01A1550A3158}" name="Item" dataDxfId="11"/>
     <tableColumn id="4" xr3:uid="{AC28EAC1-12EF-4B49-AF79-298B79DBA0E9}" name="Bank A Debit" dataDxfId="9" dataCellStyle="Currency"/>
     <tableColumn id="5" xr3:uid="{BC31F601-6029-0745-AE4C-6797D1695049}" name="Bank A Credit" dataDxfId="8" dataCellStyle="Currency"/>
     <tableColumn id="6" xr3:uid="{6C0082EE-9F37-314F-B560-646DC8B5AD7F}" name="Bank A Balance" dataDxfId="7" dataCellStyle="Currency">
@@ -1236,370 +1380,370 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46296</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2">
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>500</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2">
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8">
         <v>500</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2">
+      <c r="J2" s="6"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8">
         <v>100</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="9">
         <f>F2+I2+L2</f>
         <v>1100</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46296</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2">
+      <c r="D3" s="6"/>
+      <c r="E3" s="7">
         <v>400</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="8">
         <f>F2-D3+E3</f>
         <v>900</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2">
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8">
         <f>I2-G3+H3</f>
         <v>500</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="J3" s="6"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8">
         <f>L2-J3+K3</f>
         <v>100</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="9">
         <f t="shared" ref="M3:M10" si="0">F3+I3+L3</f>
         <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>46296</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <f t="shared" ref="F4:F10" si="1">F3-D4+E4</f>
         <v>900</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="6"/>
+      <c r="H4" s="7">
         <v>500</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="8">
         <f t="shared" ref="I4:I10" si="2">I3-G4+H4</f>
         <v>1000</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="J4" s="6"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8">
         <f t="shared" ref="L4:L10" si="3">L3-J4+K4</f>
         <v>100</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="9">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>46296</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="6">
         <v>136</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
+      <c r="H5" s="7"/>
+      <c r="I5" s="8">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="J5" s="6"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="8">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="9">
         <f t="shared" si="0"/>
         <v>1864</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>46297</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="6">
         <v>25</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <f t="shared" si="1"/>
         <v>875</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="J6" s="6"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="8">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="9">
         <f t="shared" si="0"/>
         <v>1839</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>46298</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="6">
         <v>500</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="J7" s="6"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="9">
         <f t="shared" si="0"/>
         <v>1339</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>46299</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="6">
         <v>5</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="7"/>
+      <c r="L8" s="8">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="9">
         <f t="shared" si="0"/>
         <v>1334</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>46300</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="6">
         <v>86</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
+      <c r="H9" s="7"/>
+      <c r="I9" s="8">
         <f t="shared" si="2"/>
         <v>778</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
+      <c r="J9" s="6"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="9">
         <f t="shared" si="0"/>
         <v>1248</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>46301</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2">
+        <v>372</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8">
         <f t="shared" si="2"/>
         <v>778</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
+      <c r="J10" s="6"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="9">
         <f t="shared" si="0"/>
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
